--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
@@ -15589,7 +15589,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rezago respecto a la población de 6 a 21 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:40</t>
+    <t xml:space="preserve">2026-09-07 12:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:57</t>
+    <t xml:space="preserve">2026-09-08 10:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
